--- a/data/2nd Round/Corrected/Mo_200Sb_25Se_Results Table.xlsx
+++ b/data/2nd Round/Corrected/Mo_200Sb_25Se_Results Table.xlsx
@@ -537,7 +537,7 @@
         <v>0.30894378</v>
       </c>
       <c r="H2" t="n">
-        <v>43.08390781883061</v>
+        <v>39.094</v>
       </c>
       <c r="I2" t="n">
         <v>1.934741554793868</v>
@@ -591,7 +591,7 @@
         <v>0.11388587</v>
       </c>
       <c r="H3" t="n">
-        <v>43.99773542315287</v>
+        <v>39.9232</v>
       </c>
       <c r="I3" t="n">
         <v>1.948624654779022</v>
@@ -645,7 +645,7 @@
         <v>0.09769483</v>
       </c>
       <c r="H4" t="n">
-        <v>33.73855482571398</v>
+        <v>30.6141</v>
       </c>
       <c r="I4" t="n">
         <v>0.6000584326916727</v>
@@ -699,7 +699,7 @@
         <v>0.14201983</v>
       </c>
       <c r="H5" t="n">
-        <v>36.14126459771516</v>
+        <v>32.7943</v>
       </c>
       <c r="I5" t="n">
         <v>1.143495594855657</v>
@@ -753,7 +753,7 @@
         <v>0.19922645</v>
       </c>
       <c r="H6" t="n">
-        <v>39.8749314340434</v>
+        <v>36.1822</v>
       </c>
       <c r="I6" t="n">
         <v>1.539481531687119</v>
@@ -807,7 +807,7 @@
         <v>0.05621359</v>
       </c>
       <c r="H7" t="n">
-        <v>31.11400050866929</v>
+        <v>28.2326</v>
       </c>
       <c r="I7" t="n">
         <v>0.6489668698942753</v>
@@ -861,7 +861,7 @@
         <v>0.02186623</v>
       </c>
       <c r="H8" t="n">
-        <v>27.69155522981886</v>
+        <v>25.1271</v>
       </c>
       <c r="I8" t="n">
         <v>0.1102481469409319</v>
@@ -915,7 +915,7 @@
         <v>0.02210549</v>
       </c>
       <c r="H9" t="n">
-        <v>31.49454159860232</v>
+        <v>28.5779</v>
       </c>
       <c r="I9" t="n">
         <v>0.3115077271178758</v>
@@ -969,7 +969,7 @@
         <v>0.12571858</v>
       </c>
       <c r="H10" t="n">
-        <v>38.93432378777104</v>
+        <v>35.3287</v>
       </c>
       <c r="I10" t="n">
         <v>1.241856904554398</v>
@@ -1023,7 +1023,7 @@
         <v>0.07280225</v>
       </c>
       <c r="H11" t="n">
-        <v>31.99840312862661</v>
+        <v>29.0351</v>
       </c>
       <c r="I11" t="n">
         <v>0.7045900090504822</v>
@@ -1077,7 +1077,7 @@
         <v>0.25911934</v>
       </c>
       <c r="H12" t="n">
-        <v>46.30743138689935</v>
+        <v>42.019</v>
       </c>
       <c r="I12" t="n">
         <v>2.086366784043495</v>
@@ -1131,7 +1131,7 @@
         <v>0.1352227</v>
       </c>
       <c r="H13" t="n">
-        <v>56.54368915007642</v>
+        <v>51.3073</v>
       </c>
       <c r="I13" t="n">
         <v>2.879246049862311</v>
@@ -1185,7 +1185,7 @@
         <v>0.1504827</v>
       </c>
       <c r="H14" t="n">
-        <v>36.77957736715975</v>
+        <v>33.3735</v>
       </c>
       <c r="I14" t="n">
         <v>1.287407990780199</v>

--- a/data/2nd Round/Corrected/Mo_200Sb_25Se_Results Table.xlsx
+++ b/data/2nd Round/Corrected/Mo_200Sb_25Se_Results Table.xlsx
@@ -2,23 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Corrected Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,10 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,8 +415,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -511,6 +509,16 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Rseriescm2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Rshuntcm2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -551,9 +559,6 @@
       <c r="L2" t="n">
         <v>0.00052512</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>14.574</v>
       </c>
@@ -565,6 +570,12 @@
       <c r="R2" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S2" t="n">
+        <v>9.324108183433353</v>
+      </c>
+      <c r="T2" t="n">
+        <v>66.4152829167235</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -605,9 +616,6 @@
       <c r="L3" t="n">
         <v>0.00019286</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>14.82</v>
       </c>
@@ -619,6 +627,12 @@
       <c r="R3" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S3" t="n">
+        <v>9.378826234688209</v>
+      </c>
+      <c r="T3" t="n">
+        <v>93.99360883908999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -659,9 +673,6 @@
       <c r="L4" t="n">
         <v>0.00018221</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>14.551</v>
       </c>
@@ -673,6 +684,12 @@
       <c r="R4" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S4" t="n">
+        <v>10.498285164459</v>
+      </c>
+      <c r="T4" t="n">
+        <v>23.80113454094396</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -713,9 +730,6 @@
       <c r="L5" t="n">
         <v>0.00025956</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>14.562</v>
       </c>
@@ -727,6 +741,12 @@
       <c r="R5" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S5" t="n">
+        <v>12.87200413644885</v>
+      </c>
+      <c r="T5" t="n">
+        <v>46.19441935977941</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -767,9 +787,6 @@
       <c r="L6" t="n">
         <v>0.00035023</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>14.562</v>
       </c>
@@ -781,6 +798,12 @@
       <c r="R6" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S6" t="n">
+        <v>11.29680811816508</v>
+      </c>
+      <c r="T6" t="n">
+        <v>64.58048044707289</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -821,9 +844,6 @@
       <c r="L7" t="n">
         <v>0.00010794</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>14.54</v>
       </c>
@@ -835,6 +855,12 @@
       <c r="R7" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S7" t="n">
+        <v>8.755618441329897</v>
+      </c>
+      <c r="T7" t="n">
+        <v>14.34745737998252</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -875,9 +901,6 @@
       <c r="L8" t="n">
         <v>4.365e-05</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>14.82</v>
       </c>
@@ -889,6 +912,12 @@
       <c r="R8" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S8" t="n">
+        <v>11.29379522324477</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11.58939794854865</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -929,9 +958,6 @@
       <c r="L9" t="n">
         <v>4.227e-05</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>14.554</v>
       </c>
@@ -943,6 +969,12 @@
       <c r="R9" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S9" t="n">
+        <v>4.120923795559327</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6.969692930666804</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -983,9 +1015,6 @@
       <c r="L10" t="n">
         <v>0.00022277</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>14.819</v>
       </c>
@@ -997,6 +1026,12 @@
       <c r="R10" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S10" t="n">
+        <v>8.707259156216193</v>
+      </c>
+      <c r="T10" t="n">
+        <v>40.21344994265067</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1037,9 +1072,6 @@
       <c r="L11" t="n">
         <v>0.00013836</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>14.543</v>
       </c>
@@ -1051,6 +1083,12 @@
       <c r="R11" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S11" t="n">
+        <v>11.21832368140057</v>
+      </c>
+      <c r="T11" t="n">
+        <v>20.39232771938346</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1091,9 +1129,6 @@
       <c r="L12" t="n">
         <v>0.00042908</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>14.57</v>
       </c>
@@ -1105,6 +1140,12 @@
       <c r="R12" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S12" t="n">
+        <v>8.751496600619307</v>
+      </c>
+      <c r="T12" t="n">
+        <v>112.0406611605686</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1145,9 +1186,6 @@
       <c r="L13" t="n">
         <v>0.0002039</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>14.813</v>
       </c>
@@ -1159,6 +1197,12 @@
       <c r="R13" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="S13" t="n">
+        <v>4.375147138866717</v>
+      </c>
+      <c r="T13" t="n">
+        <v>120.9253758028891</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1199,9 +1243,6 @@
       <c r="L14" t="n">
         <v>0.00027268</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>14.825</v>
       </c>
@@ -1213,7 +1254,14 @@
       <c r="R14" s="1" t="n">
         <v>46272</v>
       </c>
-    </row>
+      <c r="S14" t="n">
+        <v>9.12489697585182</v>
+      </c>
+      <c r="T14" t="n">
+        <v>32.73375247603739</v>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
